--- a/AR/AR invoice Template final.xlsx
+++ b/AR/AR invoice Template final.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\MSIG BY ALEX\AR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\MSIGSX\AR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EAE330E0-7235-4FC3-8239-E572A9632DBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA7B5F39-F9F3-4D69-A53A-8DD5071B4BD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="48" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{D3F70513-4056-4EC3-ADC2-9276ACB3237B}"/>
   </bookViews>
@@ -432,7 +432,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2195" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2195" uniqueCount="244">
   <si>
     <t>ParentKey</t>
   </si>
@@ -1161,6 +1161,9 @@
   </si>
   <si>
     <t>200000</t>
+  </si>
+  <si>
+    <t>ON00</t>
   </si>
 </sst>
 </file>
@@ -10683,7 +10686,7 @@
         <v>17</v>
       </c>
       <c r="G21" s="43" t="s">
-        <v>218</v>
+        <v>243</v>
       </c>
       <c r="H21" s="42" t="s">
         <v>18</v>

--- a/AR/AR invoice Template final.xlsx
+++ b/AR/AR invoice Template final.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\MSIGSX\AR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\e y ka dai\MSIGSX\AR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA7B5F39-F9F3-4D69-A53A-8DD5071B4BD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55C929E2-4625-4A5F-A747-32123991CCF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="48" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{D3F70513-4056-4EC3-ADC2-9276ACB3237B}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{D3F70513-4056-4EC3-ADC2-9276ACB3237B}"/>
   </bookViews>
   <sheets>
     <sheet name="AR invoice Head 12.05" sheetId="2" r:id="rId1"/>
@@ -432,7 +432,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2195" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2207" uniqueCount="256">
   <si>
     <t>ParentKey</t>
   </si>
@@ -1164,6 +1164,42 @@
   </si>
   <si>
     <t>ON00</t>
+  </si>
+  <si>
+    <t>(ຈຳເປັນຕ້ອງໃສ່ຈະຫລອດບໍ່ມີປ່ຽນ)</t>
+  </si>
+  <si>
+    <t>(ຈະປ່ຽນໄປຕາມແຕ່ລະເດືອນຈ້ອງເບິ່ງໃນລະບົບຕື່ມ)</t>
+  </si>
+  <si>
+    <t>ເລກທີ່ເອກະສານ</t>
+  </si>
+  <si>
+    <t>ລະຫັດຊຸດຂໍ້ມູນ</t>
+  </si>
+  <si>
+    <t>ປະເພດເອກະສານ</t>
+  </si>
+  <si>
+    <t>ວັນທີບັນທຶກເອກະສານ</t>
+  </si>
+  <si>
+    <t>ວັນຄົບກຳນົດການຊຳລະ</t>
+  </si>
+  <si>
+    <t>ລະຫັດຄູ່ຄ້າ</t>
+  </si>
+  <si>
+    <t>ຍອດລວມຂອງເອກະສານ</t>
+  </si>
+  <si>
+    <t>ວັນຄຳນວນ Tax</t>
+  </si>
+  <si>
+    <t>ເລກທີ່ສັນຍາ</t>
+  </si>
+  <si>
+    <t>ຊື່ຜູ້ອອກສັນຍາ</t>
   </si>
 </sst>
 </file>
@@ -1171,15 +1207,23 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="187" formatCode="yyyymmdd"/>
+    <numFmt numFmtId="187" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="188" formatCode="yyyymmdd"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Tahoma"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <charset val="222"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1274,8 +1318,20 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Phetsarath OT"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1309,6 +1365,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1352,156 +1420,168 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="187" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="187" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="187" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="188" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="187" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="187" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="187" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="187" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="187" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="188" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="14" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="13" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="14" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="14" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="13" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="16" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="12" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="15" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="43" fontId="11" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="187" fontId="12" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="187" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="187" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="188" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="188" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="2" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="10" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="11" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="43" fontId="10" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="187" fontId="11" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="10" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="187" fontId="11" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="187" fontId="10" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="188" fontId="11" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="10" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="187" fontId="11" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="43" fontId="11" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="187" fontId="12" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="10" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="187" fontId="11" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="10" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="187" fontId="11" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="187" fontId="10" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="188" fontId="11" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="10" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="11" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 3" xfId="1" xr:uid="{B6A03B44-5BAE-480A-9FC5-65F600ADEDAD}"/>
+    <cellStyle name="Normal 3 2" xfId="2" xr:uid="{454BE4C8-1811-4F80-B3D8-BCCADE7E7F8E}"/>
   </cellStyles>
   <dxfs count="3">
     <dxf>
@@ -1857,14 +1937,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21AA6997-1446-4B2C-AB06-1FD8E024F25E}">
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.19921875" customWidth="1"/>
-    <col min="6" max="6" width="9.59765625" customWidth="1"/>
-    <col min="7" max="7" width="12.8984375" customWidth="1"/>
-    <col min="11" max="11" width="20.09765625" customWidth="1"/>
-    <col min="12" max="12" width="17.59765625" customWidth="1"/>
+    <col min="1" max="1" width="12.59765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.69921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.3984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.3984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.09765625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.8984375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="34.09765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -1943,8 +2030,8 @@
         <v>237</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="15" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="60" t="s">
         <v>203</v>
       </c>
       <c r="B3">
@@ -1976,8 +2063,8 @@
         <v>165</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="15" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="60" t="s">
         <v>204</v>
       </c>
       <c r="B4">
@@ -2009,8 +2096,8 @@
         <v>193</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="15" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="60" t="s">
         <v>205</v>
       </c>
       <c r="B5">
@@ -2042,8 +2129,8 @@
         <v>202</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="15" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="61" t="s">
         <v>221</v>
       </c>
       <c r="B6">
@@ -2074,8 +2161,8 @@
         <v>202</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="15" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="61" t="s">
         <v>222</v>
       </c>
       <c r="B7">
@@ -2106,8 +2193,8 @@
         <v>165</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="15" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="61" t="s">
         <v>223</v>
       </c>
       <c r="B8">
@@ -2138,8 +2225,8 @@
         <v>193</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="15" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="61" t="s">
         <v>224</v>
       </c>
       <c r="B9">
@@ -2170,8 +2257,8 @@
         <v>202</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="15" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="61" t="s">
         <v>225</v>
       </c>
       <c r="B10">
@@ -2202,8 +2289,8 @@
         <v>165</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="15" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="61" t="s">
         <v>226</v>
       </c>
       <c r="B11">
@@ -2234,8 +2321,8 @@
         <v>193</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="15" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" s="61" t="s">
         <v>227</v>
       </c>
       <c r="B12">
@@ -2266,8 +2353,48 @@
         <v>202</v>
       </c>
     </row>
+    <row r="13" spans="1:12" ht="18.600000000000001" x14ac:dyDescent="0.5">
+      <c r="A13" s="62" t="s">
+        <v>246</v>
+      </c>
+      <c r="B13" s="62" t="s">
+        <v>247</v>
+      </c>
+      <c r="C13" s="62" t="s">
+        <v>248</v>
+      </c>
+      <c r="D13" s="62" t="s">
+        <v>249</v>
+      </c>
+      <c r="E13" s="62" t="s">
+        <v>250</v>
+      </c>
+      <c r="F13" s="62" t="s">
+        <v>253</v>
+      </c>
+      <c r="G13" s="62" t="s">
+        <v>251</v>
+      </c>
+      <c r="H13" s="62" t="s">
+        <v>252</v>
+      </c>
+      <c r="K13" s="62" t="s">
+        <v>255</v>
+      </c>
+      <c r="L13" s="62" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="18.600000000000001" x14ac:dyDescent="0.5">
+      <c r="B15" s="59" t="s">
+        <v>245</v>
+      </c>
+      <c r="C15" s="59" t="s">
+        <v>244</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="K3:K5">
     <cfRule type="expression" dxfId="2" priority="1">
       <formula>ISNUMBER(MATCH(K3,$DJ:$DJ,0))</formula>
@@ -2286,7 +2413,7 @@
     <col min="13" max="13" width="13" style="34"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:139" s="25" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:139" s="25" customFormat="1" ht="15.6" x14ac:dyDescent="0.4">
       <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
@@ -2705,7 +2832,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="2" spans="1:139" s="25" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:139" s="25" customFormat="1" ht="15.6" x14ac:dyDescent="0.4">
       <c r="A2" s="31" t="s">
         <v>11</v>
       </c>
@@ -3124,7 +3251,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="3" spans="1:139" s="58" customFormat="1" ht="16.8" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:139" s="58" customFormat="1" ht="15.6" x14ac:dyDescent="0.4">
       <c r="A3" s="41" t="s">
         <v>203</v>
       </c>
@@ -3543,7 +3670,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="4" spans="1:139" ht="16.8" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:139" ht="15.6" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>203</v>
       </c>
@@ -3962,7 +4089,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="5" spans="1:139" ht="16.8" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:139" ht="15.6" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>203</v>
       </c>
@@ -4381,7 +4508,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="6" spans="1:139" s="58" customFormat="1" ht="16.8" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:139" s="58" customFormat="1" ht="15.6" x14ac:dyDescent="0.4">
       <c r="A6" s="41" t="s">
         <v>204</v>
       </c>
@@ -4800,7 +4927,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="7" spans="1:139" ht="16.8" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:139" ht="15.6" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
         <v>204</v>
       </c>
@@ -5219,7 +5346,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="8" spans="1:139" ht="16.8" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:139" ht="15.6" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
         <v>204</v>
       </c>
@@ -5638,7 +5765,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="9" spans="1:139" s="58" customFormat="1" ht="16.8" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:139" s="58" customFormat="1" ht="15.6" x14ac:dyDescent="0.4">
       <c r="A9" s="41" t="s">
         <v>205</v>
       </c>
@@ -6057,7 +6184,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="10" spans="1:139" ht="16.8" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:139" ht="15.6" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
         <v>205</v>
       </c>
@@ -6476,7 +6603,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="11" spans="1:139" ht="16.8" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:139" ht="15.6" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
         <v>205</v>
       </c>
@@ -6895,7 +7022,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="12" spans="1:139" s="58" customFormat="1" ht="16.8" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:139" s="58" customFormat="1" ht="15.6" x14ac:dyDescent="0.4">
       <c r="A12" s="41" t="s">
         <v>221</v>
       </c>
@@ -7314,7 +7441,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="13" spans="1:139" ht="16.8" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:139" ht="15.6" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
         <v>221</v>
       </c>
@@ -7733,7 +7860,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="14" spans="1:139" ht="16.8" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:139" ht="15.6" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
         <v>221</v>
       </c>
@@ -8152,7 +8279,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="15" spans="1:139" s="58" customFormat="1" ht="16.8" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:139" s="58" customFormat="1" ht="15.6" x14ac:dyDescent="0.4">
       <c r="A15" s="41" t="s">
         <v>222</v>
       </c>
@@ -8571,7 +8698,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="16" spans="1:139" ht="16.8" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:139" ht="15.6" x14ac:dyDescent="0.4">
       <c r="A16" s="1" t="s">
         <v>222</v>
       </c>
@@ -8990,7 +9117,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="17" spans="1:139" ht="16.8" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:139" ht="15.6" x14ac:dyDescent="0.4">
       <c r="A17" s="1" t="s">
         <v>222</v>
       </c>
@@ -9409,7 +9536,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="18" spans="1:139" s="58" customFormat="1" ht="16.8" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:139" s="58" customFormat="1" ht="15.6" x14ac:dyDescent="0.4">
       <c r="A18" s="41" t="s">
         <v>223</v>
       </c>
@@ -9828,7 +9955,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="19" spans="1:139" ht="16.8" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:139" ht="15.6" x14ac:dyDescent="0.4">
       <c r="A19" s="1" t="s">
         <v>223</v>
       </c>
@@ -10247,7 +10374,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="20" spans="1:139" ht="16.8" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:139" ht="15.6" x14ac:dyDescent="0.4">
       <c r="A20" s="1" t="s">
         <v>223</v>
       </c>
@@ -10666,7 +10793,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="21" spans="1:139" s="58" customFormat="1" ht="16.8" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:139" s="58" customFormat="1" ht="15.6" x14ac:dyDescent="0.4">
       <c r="A21" s="41" t="s">
         <v>224</v>
       </c>
@@ -11085,7 +11212,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="22" spans="1:139" ht="16.8" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:139" ht="15.6" x14ac:dyDescent="0.4">
       <c r="A22" s="1" t="s">
         <v>224</v>
       </c>
@@ -11504,7 +11631,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="23" spans="1:139" ht="16.8" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:139" ht="15.6" x14ac:dyDescent="0.4">
       <c r="A23" s="1" t="s">
         <v>224</v>
       </c>
@@ -11923,7 +12050,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="24" spans="1:139" s="58" customFormat="1" ht="16.8" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:139" s="58" customFormat="1" ht="15.6" x14ac:dyDescent="0.4">
       <c r="A24" s="41" t="s">
         <v>225</v>
       </c>
@@ -12342,7 +12469,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="25" spans="1:139" ht="16.8" x14ac:dyDescent="0.5">
+    <row r="25" spans="1:139" ht="15.6" x14ac:dyDescent="0.4">
       <c r="A25" s="1" t="s">
         <v>225</v>
       </c>
@@ -12761,7 +12888,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="26" spans="1:139" ht="16.8" x14ac:dyDescent="0.5">
+    <row r="26" spans="1:139" ht="15.6" x14ac:dyDescent="0.4">
       <c r="A26" s="1" t="s">
         <v>225</v>
       </c>
@@ -13180,7 +13307,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="27" spans="1:139" s="58" customFormat="1" ht="16.8" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:139" s="58" customFormat="1" ht="15.6" x14ac:dyDescent="0.4">
       <c r="A27" s="41" t="s">
         <v>226</v>
       </c>
@@ -13599,7 +13726,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="28" spans="1:139" ht="16.8" x14ac:dyDescent="0.5">
+    <row r="28" spans="1:139" ht="15.6" x14ac:dyDescent="0.4">
       <c r="A28" s="1" t="s">
         <v>226</v>
       </c>
@@ -14018,7 +14145,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="29" spans="1:139" ht="16.8" x14ac:dyDescent="0.5">
+    <row r="29" spans="1:139" ht="15.6" x14ac:dyDescent="0.4">
       <c r="A29" s="1" t="s">
         <v>226</v>
       </c>
@@ -14437,7 +14564,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="30" spans="1:139" s="58" customFormat="1" ht="16.8" x14ac:dyDescent="0.5">
+    <row r="30" spans="1:139" s="58" customFormat="1" ht="15.6" x14ac:dyDescent="0.4">
       <c r="A30" s="41" t="s">
         <v>227</v>
       </c>
@@ -14856,7 +14983,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="31" spans="1:139" ht="16.8" x14ac:dyDescent="0.5">
+    <row r="31" spans="1:139" ht="15.6" x14ac:dyDescent="0.4">
       <c r="A31" s="1" t="s">
         <v>227</v>
       </c>
@@ -15275,7 +15402,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="32" spans="1:139" ht="16.8" x14ac:dyDescent="0.5">
+    <row r="32" spans="1:139" ht="15.6" x14ac:dyDescent="0.4">
       <c r="A32" s="1" t="s">
         <v>227</v>
       </c>
@@ -15696,7 +15823,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A2:EI32" xr:uid="{652C9FD0-27CA-4A8C-A356-B1E77E4D7898}"/>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="O3:O32">
     <cfRule type="expression" dxfId="1" priority="1">
       <formula>ISNUMBER(MATCH(O3,$DK:$DK,0))</formula>
